--- a/BAT01N.xlsx
+++ b/BAT01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="171">
   <si>
     <t/>
   </si>
@@ -97,6 +97,21 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>20140180</t>
+  </si>
+  <si>
+    <t>ABC ALKALINE AA 8'S</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20071089</t>
+  </si>
+  <si>
+    <t>ENRGIZER 3V 2032 2'S</t>
+  </si>
+  <si>
     <t>10015438</t>
   </si>
   <si>
@@ -133,58 +148,112 @@
     <t>PANASONIC AA LR 6T2B</t>
   </si>
   <si>
+    <t>10025645</t>
+  </si>
+  <si>
+    <t>ABC ALKALINE 9 VOLT</t>
+  </si>
+  <si>
+    <t>10000313</t>
+  </si>
+  <si>
+    <t>ABC ALK AAA-LR03/2MP</t>
+  </si>
+  <si>
+    <t>10006334</t>
+  </si>
+  <si>
+    <t>ABC LR03-AAA/4S MPWR</t>
+  </si>
+  <si>
+    <t>10005660</t>
+  </si>
+  <si>
+    <t>ABC ALKALIN AA-LR6/2</t>
+  </si>
+  <si>
+    <t>10005662</t>
+  </si>
+  <si>
+    <t>ABC ALKALIN AA-LR6/4</t>
+  </si>
+  <si>
     <t>20120510</t>
   </si>
   <si>
     <t>EVREADY LED MTL LIGH</t>
   </si>
   <si>
-    <t>20071089</t>
-  </si>
-  <si>
-    <t>ENRGIZER 3V 2032 2'S</t>
-  </si>
-  <si>
     <t>20134319</t>
   </si>
   <si>
     <t>ENRGIZER 3V 2016 2'S</t>
   </si>
   <si>
-    <t>10005662</t>
-  </si>
-  <si>
-    <t>ABC ALKALIN AA-LR6/4</t>
-  </si>
-  <si>
-    <t>10005660</t>
-  </si>
-  <si>
-    <t>ABC ALKALIN AA-LR6/2</t>
-  </si>
-  <si>
-    <t>10006334</t>
-  </si>
-  <si>
-    <t>ABC LR03-AAA/4S MPWR</t>
-  </si>
-  <si>
-    <t>10000313</t>
-  </si>
-  <si>
-    <t>ABC ALK AAA-LR03/2MP</t>
-  </si>
-  <si>
-    <t>20140180</t>
-  </si>
-  <si>
-    <t>ABC ALKALINE AA 8'S</t>
-  </si>
-  <si>
-    <t>10025645</t>
-  </si>
-  <si>
-    <t>ABC ALKALINE 9 VOLT</t>
+    <t>20085748</t>
+  </si>
+  <si>
+    <t>NXCARE CRBN MASK 2'S</t>
+  </si>
+  <si>
+    <t>20130057</t>
+  </si>
+  <si>
+    <t>AMRA NAIL PL PRPLE 5</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20130070</t>
+  </si>
+  <si>
+    <t>AMRA LPSTK STR PN2.2</t>
+  </si>
+  <si>
+    <t>20131278</t>
+  </si>
+  <si>
+    <t>IDM DUCKBILL PTIH 4S</t>
+  </si>
+  <si>
+    <t>20131301</t>
+  </si>
+  <si>
+    <t>IDM DUCKBILL HTAM 4S</t>
+  </si>
+  <si>
+    <t>20111707</t>
+  </si>
+  <si>
+    <t>IDM MASKER 4D PTH 4S</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
+  </si>
+  <si>
+    <t>20130058</t>
+  </si>
+  <si>
+    <t>AMRA NAIL BLRN.PNK 5</t>
+  </si>
+  <si>
+    <t>20130068</t>
+  </si>
+  <si>
+    <t>AMRA LPSTK AVO CR2.2</t>
+  </si>
+  <si>
+    <t>20115472</t>
+  </si>
+  <si>
+    <t>IDM MASK 4D HTM 4'S</t>
   </si>
   <si>
     <t>20117862</t>
@@ -193,64 +262,16 @@
     <t>IDM MASKER PCK 5'S</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20120506</t>
   </si>
   <si>
     <t>IDM MASKER HIJAB 5'S</t>
   </si>
   <si>
-    <t>20085748</t>
-  </si>
-  <si>
-    <t>NXCARE CRBN MASK 2'S</t>
-  </si>
-  <si>
-    <t>20111707</t>
-  </si>
-  <si>
-    <t>IDM MASKER 4D PTH 4S</t>
-  </si>
-  <si>
-    <t>20115472</t>
-  </si>
-  <si>
-    <t>IDM MASK 4D HTM 4'S</t>
-  </si>
-  <si>
-    <t>20131278</t>
-  </si>
-  <si>
-    <t>IDM DUCKBILL PTIH 4S</t>
-  </si>
-  <si>
-    <t>20131301</t>
-  </si>
-  <si>
-    <t>IDM DUCKBILL HTAM 4S</t>
-  </si>
-  <si>
-    <t>20130057</t>
-  </si>
-  <si>
-    <t>AMRA NAIL PL PRPLE 5</t>
-  </si>
-  <si>
-    <t>20130058</t>
-  </si>
-  <si>
-    <t>AMRA NAIL BLRN.PNK 5</t>
+    <t>20130071</t>
+  </si>
+  <si>
+    <t>AMARA MAKE UP KIT</t>
   </si>
   <si>
     <t>20130060</t>
@@ -259,25 +280,52 @@
     <t>AMRA NAIL BLSM.PNK 5</t>
   </si>
   <si>
-    <t>20130068</t>
-  </si>
-  <si>
-    <t>AMRA LPSTK AVO CR2.2</t>
-  </si>
-  <si>
-    <t>20130070</t>
-  </si>
-  <si>
-    <t>AMRA LPSTK STR PN2.2</t>
-  </si>
-  <si>
-    <t>20130071</t>
-  </si>
-  <si>
-    <t>AMARA MAKE UP KIT</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>20129265</t>
+  </si>
+  <si>
+    <t>PKMON KRT.VIOLT SV1V</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20138219</t>
+  </si>
+  <si>
+    <t>ONE PIECE TRAD.CARD</t>
+  </si>
+  <si>
+    <t>PT,(E-70B)</t>
+  </si>
+  <si>
+    <t>20134835</t>
+  </si>
+  <si>
+    <t>MONSTA BOBOI GLX CRD</t>
+  </si>
+  <si>
+    <t>20132246</t>
+  </si>
+  <si>
+    <t>POKEMON GM KRT SVDS</t>
+  </si>
+  <si>
+    <t>20107146</t>
+  </si>
+  <si>
+    <t>UNO EXPRESS</t>
+  </si>
+  <si>
+    <t>10035016</t>
+  </si>
+  <si>
+    <t>KARTU REMI PCS</t>
+  </si>
+  <si>
+    <t>10003939</t>
+  </si>
+  <si>
+    <t>KARTU DOMINO PCS</t>
   </si>
   <si>
     <t>20129264</t>
@@ -286,13 +334,34 @@
     <t>PKEMON KRT.SCAR SV1S</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20129265</t>
-  </si>
-  <si>
-    <t>PKMON KRT.VIOLT SV1V</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20129925</t>
+  </si>
+  <si>
+    <t>POKEMON KARTU SV1A</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20130598</t>
+  </si>
+  <si>
+    <t>POKEMON KRT SV2A 151</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20132780</t>
+  </si>
+  <si>
+    <t>POKEMON KARTU SV4S</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>20131793</t>
@@ -301,10 +370,7 @@
     <t>POKEMON KARTU SV3S</t>
   </si>
   <si>
-    <t>20132780</t>
-  </si>
-  <si>
-    <t>POKEMON KARTU SV4S</t>
+    <t>16</t>
   </si>
   <si>
     <t>20134165</t>
@@ -313,58 +379,88 @@
     <t>POKEMON SET SPC SV5S</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20120831</t>
+  </si>
+  <si>
+    <t>POKEMON GM KARTU-12</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20135818</t>
+  </si>
+  <si>
+    <t>UNO C/GM FLIP EXPRES</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20129926</t>
+  </si>
+  <si>
+    <t>POKEMON KARTU SV2D</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20129927</t>
+  </si>
+  <si>
+    <t>POKEMON KARTU SV2P</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>20134684</t>
   </si>
   <si>
     <t>POKEMON SET SV6S-P</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20134862</t>
+  </si>
+  <si>
+    <t>FF CLLCTBLE TRDG CRD</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>20135608</t>
   </si>
   <si>
     <t>POKEMON SET SPC SV7S</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20136622</t>
+  </si>
+  <si>
+    <t>ONE PIECE COLEC.CARD</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>20136710</t>
   </si>
   <si>
     <t>POKEMON SPC KLT RS2S</t>
   </si>
   <si>
-    <t>20129925</t>
-  </si>
-  <si>
-    <t>POKEMON KARTU SV1A</t>
-  </si>
-  <si>
-    <t>20129926</t>
-  </si>
-  <si>
-    <t>POKEMON KARTU SV2D</t>
-  </si>
-  <si>
-    <t>20129927</t>
-  </si>
-  <si>
-    <t>POKEMON KARTU SV2P</t>
-  </si>
-  <si>
-    <t>20132246</t>
-  </si>
-  <si>
-    <t>POKEMON GM KRT SVDS</t>
-  </si>
-  <si>
-    <t>20134862</t>
-  </si>
-  <si>
-    <t>FF CLLCTBLE TRDG CRD</t>
-  </si>
-  <si>
-    <t>20136622</t>
-  </si>
-  <si>
-    <t>ONE PIECE COLEC.CARD</t>
+    <t>27</t>
   </si>
   <si>
     <t>20137834</t>
@@ -373,85 +469,55 @@
     <t>PANINI ADRENALYN XL</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>20138906</t>
   </si>
   <si>
     <t>MONSTA GALAXY CARD</t>
   </si>
   <si>
-    <t>20107146</t>
-  </si>
-  <si>
-    <t>UNO EXPRESS</t>
-  </si>
-  <si>
-    <t>20134835</t>
-  </si>
-  <si>
-    <t>MONSTA BOBOI GLX CRD</t>
-  </si>
-  <si>
-    <t>20135818</t>
-  </si>
-  <si>
-    <t>UNO C/GM FLIP EXPRES</t>
-  </si>
-  <si>
-    <t>10035016</t>
-  </si>
-  <si>
-    <t>KARTU REMI PCS</t>
-  </si>
-  <si>
-    <t>10003939</t>
-  </si>
-  <si>
-    <t>KARTU DOMINO PCS</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20101309</t>
+  </si>
+  <si>
+    <t>POKEMON GM KARTU-5</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
+    <t>20110458</t>
+  </si>
+  <si>
+    <t>POKEMON GM KARTU-6</t>
+  </si>
+  <si>
+    <t>20113829</t>
+  </si>
+  <si>
+    <t>POKEMON GM KARTU-7</t>
+  </si>
+  <si>
+    <t>20116681</t>
+  </si>
+  <si>
+    <t>POKEMON GM KARTU-9</t>
+  </si>
+  <si>
+    <t>20119279</t>
+  </si>
+  <si>
+    <t>POKEMON GM KARTU-10</t>
   </si>
   <si>
     <t>20122811</t>
   </si>
   <si>
     <t>POKEMON GM KARTU-13</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>20120831</t>
-  </si>
-  <si>
-    <t>POKEMON GM KARTU-12</t>
-  </si>
-  <si>
-    <t>20116681</t>
-  </si>
-  <si>
-    <t>POKEMON GM KARTU-9</t>
-  </si>
-  <si>
-    <t>20113829</t>
-  </si>
-  <si>
-    <t>POKEMON GM KARTU-7</t>
-  </si>
-  <si>
-    <t>20119279</t>
-  </si>
-  <si>
-    <t>POKEMON GM KARTU-10</t>
-  </si>
-  <si>
-    <t>20101309</t>
-  </si>
-  <si>
-    <t>POKEMON GM KARTU-5</t>
-  </si>
-  <si>
-    <t>20110458</t>
-  </si>
-  <si>
-    <t>POKEMON GM KARTU-6</t>
   </si>
   <si>
     <t>20124062</t>
@@ -850,15 +916,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1052,10 +1118,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -1063,10 +1129,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1075,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1083,10 +1149,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1095,7 +1161,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1103,10 +1169,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1115,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1123,10 +1189,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1135,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1143,10 +1209,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1155,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1163,10 +1229,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1175,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1183,19 +1249,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1203,10 +1269,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1218,15 +1284,15 @@
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1243,10 +1309,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1263,10 +1329,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1283,10 +1349,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1303,10 +1369,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1315,7 +1381,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1323,10 +1389,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1335,18 +1401,18 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1358,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1398,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,10 +1481,10 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1435,10 +1501,10 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1458,15 +1524,15 @@
         <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1483,10 +1549,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1503,10 +1569,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1515,7 +1581,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>63</v>
@@ -1523,10 +1589,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1535,18 +1601,18 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1555,18 +1621,18 @@
         <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1575,18 +1641,18 @@
         <v>14</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1595,7 +1661,7 @@
         <v>14</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>63</v>
@@ -1603,10 +1669,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1615,7 +1681,7 @@
         <v>14</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>63</v>
@@ -1635,7 +1701,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>91</v>
@@ -1655,18 +1721,18 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1675,7 +1741,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>91</v>
@@ -1683,10 +1749,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1695,7 +1761,7 @@
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>91</v>
@@ -1703,10 +1769,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1715,7 +1781,7 @@
         <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>91</v>
@@ -1723,10 +1789,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1735,18 +1801,18 @@
         <v>17</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1755,18 +1821,18 @@
         <v>17</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1775,7 +1841,7 @@
         <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>91</v>
@@ -1783,10 +1849,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1795,7 +1861,7 @@
         <v>17</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>91</v>
@@ -1803,10 +1869,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1815,7 +1881,7 @@
         <v>17</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>91</v>
@@ -1823,10 +1889,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1835,18 +1901,18 @@
         <v>17</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -1855,7 +1921,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>91</v>
@@ -1863,10 +1929,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -1875,7 +1941,7 @@
         <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>91</v>
@@ -1883,10 +1949,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -1895,7 +1961,7 @@
         <v>17</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>91</v>
@@ -1903,10 +1969,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -1915,7 +1981,7 @@
         <v>17</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>91</v>
@@ -1923,10 +1989,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -1935,18 +2001,18 @@
         <v>17</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -1955,18 +2021,18 @@
         <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -1975,7 +2041,7 @@
         <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>91</v>
@@ -1983,10 +2049,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -1995,7 +2061,7 @@
         <v>17</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>91</v>
@@ -2003,10 +2069,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2015,18 +2081,18 @@
         <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2035,27 +2101,27 @@
         <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>149</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>91</v>
@@ -2063,19 +2129,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>91</v>
@@ -2083,39 +2149,39 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>155</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>91</v>
@@ -2123,19 +2189,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>91</v>
@@ -2143,19 +2209,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>91</v>
@@ -2163,19 +2229,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>91</v>
@@ -2183,21 +2249,61 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F67" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>91</v>
       </c>
     </row>

--- a/BAT01N.xlsx
+++ b/BAT01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="173">
   <si>
     <t/>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>AMRA NAIL BLSM.PNK 5</t>
+  </si>
+  <si>
+    <t>20142764</t>
+  </si>
+  <si>
+    <t>IDM MSKR SLIM PTH 5S</t>
   </si>
   <si>
     <t>20129265</t>
@@ -916,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1698,22 +1704,22 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
@@ -1721,30 +1727,30 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1761,10 +1767,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1781,10 +1787,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1801,10 +1807,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,7 +1827,7 @@
         <v>17</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1841,370 +1847,370 @@
         <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="F56" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F63" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2218,13 +2224,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2238,13 +2244,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2258,13 +2264,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2278,13 +2284,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2298,13 +2304,33 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>91</v>
+      <c r="F70" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
